--- a/verification/report-samples/drivers-full-field.xlsx
+++ b/verification/report-samples/drivers-full-field.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Full-field register" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$T5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$Y7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Full-field register'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -23,64 +23,79 @@
     <t>Selected period 2026-01-01 to 2026-12-31; current master records; loans cumulative through cutoff including opening principal.</t>
   </si>
   <si>
-    <t>vehical no</t>
-  </si>
-  <si>
-    <t>driver name</t>
-  </si>
-  <si>
-    <t>father name</t>
-  </si>
-  <si>
-    <t>cnic no</t>
-  </si>
-  <si>
-    <t>driving license no</t>
-  </si>
-  <si>
-    <t>mobile no</t>
-  </si>
-  <si>
-    <t>next of kin no</t>
-  </si>
-  <si>
-    <t>joining date</t>
-  </si>
-  <si>
-    <t>leaving date</t>
-  </si>
-  <si>
-    <t>adress</t>
-  </si>
-  <si>
-    <t>tool</t>
-  </si>
-  <si>
-    <t>pp</t>
-  </si>
-  <si>
-    <t>liter</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>ave</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>cycle</t>
-  </si>
-  <si>
-    <t>loan taken</t>
-  </si>
-  <si>
-    <t>loan paid</t>
-  </si>
-  <si>
-    <t>loan left</t>
+    <t>Assigned vehicle</t>
+  </si>
+  <si>
+    <t>Vehicle assigned date</t>
+  </si>
+  <si>
+    <t>Assignment reason (optional)</t>
+  </si>
+  <si>
+    <t>Driver name</t>
+  </si>
+  <si>
+    <t>Father’s name</t>
+  </si>
+  <si>
+    <t>CNIC number</t>
+  </si>
+  <si>
+    <t>Driving licence number</t>
+  </si>
+  <si>
+    <t>Mobile number</t>
+  </si>
+  <si>
+    <t>Next of kin number</t>
+  </si>
+  <si>
+    <t>Joining date</t>
+  </si>
+  <si>
+    <t>Leaving date</t>
+  </si>
+  <si>
+    <t>Licence expiry</t>
+  </si>
+  <si>
+    <t>Employment status</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Tolls (PKR)</t>
+  </si>
+  <si>
+    <t>Punjab Police (PKR)</t>
+  </si>
+  <si>
+    <t>Matched fuel (litres)</t>
+  </si>
+  <si>
+    <t>Total distance (km)</t>
+  </si>
+  <si>
+    <t>Average (km/L)</t>
+  </si>
+  <si>
+    <t>Cargo weight (tonnes)</t>
+  </si>
+  <si>
+    <t>Completed trips</t>
+  </si>
+  <si>
+    <t>Total loan (PKR)</t>
+  </si>
+  <si>
+    <t>Loan repaid (PKR)</t>
+  </si>
+  <si>
+    <t>Loan balance (PKR)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
   <si>
     <t>TEST-001</t>
@@ -102,10 +117,16 @@
   </si>
   <si>
     <t>03000000002</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
   <si>
     <t xml:space="preserve">TEST address with
 second line</t>
+  </si>
+  <si>
+    <t>Signature: __________________________</t>
   </si>
 </sst>
 </file>
@@ -240,7 +261,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -605,73 +626,93 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="1" customWidth="1"/>
-    <col min="6" max="7" width="22" style="1" customWidth="1"/>
-    <col min="8" max="9" width="22" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22" style="1" customWidth="1"/>
-    <col min="11" max="12" width="22" style="3" customWidth="1"/>
-    <col min="13" max="16" width="22" style="4" customWidth="1"/>
-    <col min="17" max="17" width="22" style="5" customWidth="1"/>
-    <col min="18" max="20" width="22" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30" style="1" customWidth="1"/>
+    <col min="4" max="6" width="22" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="1" customWidth="1"/>
+    <col min="9" max="9" width="30" style="1" customWidth="1"/>
+    <col min="10" max="12" width="22" style="2" customWidth="1"/>
+    <col min="13" max="13" width="30" style="1" customWidth="1"/>
+    <col min="14" max="14" width="22" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22" style="3" customWidth="1"/>
+    <col min="16" max="16" width="30" style="3" customWidth="1"/>
+    <col min="17" max="18" width="30" style="4" customWidth="1"/>
+    <col min="19" max="19" width="22" style="4" customWidth="1"/>
+    <col min="20" max="20" width="30" style="4" customWidth="1"/>
+    <col min="21" max="21" width="22" style="5" customWidth="1"/>
+    <col min="22" max="22" width="22" style="3" customWidth="1"/>
+    <col min="23" max="24" width="30" style="3" customWidth="1"/>
+    <col min="25" max="25" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="7"/>
     </row>
-    <row r="2" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="13"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="40" customHeight="1" spans="1:25" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="19" t="s">
@@ -689,108 +730,161 @@
       <c r="G4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="O4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="22" t="s">
+      <c r="P4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="21" t="s">
+      <c r="T4" s="22" t="s">
         <v>21</v>
       </c>
+      <c r="U4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>24</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46306</v>
+      </c>
+      <c r="C5" s="13"/>
       <c r="D5" s="13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="14">
+        <v>31</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="14">
         <v>46023</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="15">
         <v>3000</v>
       </c>
-      <c r="L5" s="15">
+      <c r="P5" s="15">
         <v>0</v>
       </c>
-      <c r="M5" s="16">
+      <c r="Q5" s="16">
         <v>68</v>
       </c>
-      <c r="N5" s="16">
+      <c r="R5" s="16">
         <v>538</v>
       </c>
-      <c r="O5" s="16">
+      <c r="S5" s="16">
         <v>7.91</v>
       </c>
-      <c r="P5" s="16">
+      <c r="T5" s="16">
         <v>12.345</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="U5" s="17">
         <v>1</v>
       </c>
-      <c r="R5" s="15">
+      <c r="V5" s="15">
         <v>50000</v>
       </c>
-      <c r="S5" s="15">
+      <c r="W5" s="15">
         <v>15000</v>
       </c>
-      <c r="T5" s="15">
+      <c r="X5" s="15">
         <v>35000</v>
       </c>
+      <c r="Y5" s="13"/>
+    </row>
+    <row r="7" spans="1:25" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T4"/>
+  <autoFilter ref="A4:Y4"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
